--- a/web/public/tools/files/k-conmap-wonclick.xlsx
+++ b/web/public/tools/files/k-conmap-wonclick.xlsx
@@ -43,7 +43,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'03 계약보증금 지급각서'!$A$1:$M$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'04 청렴계약 이행서약서'!$A$1:$M$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'05 수의계약 각서'!$A$1:$M$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'06 착공신고서'!$A$1:$M$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'06 착공신고서'!$A$1:$M$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'07 현장대리인계'!$A$1:$M$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'08 예정공정표'!$A$1:$M$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'09 직접시공계획서'!$A$1:$M$30</definedName>
@@ -59,7 +59,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="20">'19 하자보수보증금 지급각서'!$A$1:$M$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'20 공사감독조서'!$A$1:$M$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'21 준공검사조서'!$A$1:$M$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="23">'22 공사대장'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'22 공사대장'!$A$1:$M$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="24">'23 하자검사조서'!$A$1:$M$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="25">'24 하자대장'!$A$1:$M$24</definedName>
   </definedNames>
@@ -3108,7 +3108,7 @@
       <c r="C7" s="36" t="n"/>
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="38">
-        <f>IF(OR('입력'!$C$12="",'입력'!$C$13=""),"",IF('입력'!$C$12="","",YEAR('입력'!$C$12)&amp;". "&amp;MONTH('입력'!$C$12)&amp;". "&amp;DAY('입력'!$C$12)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$13="","",YEAR('입력'!$C$13)&amp;". "&amp;MONTH('입력'!$C$13)&amp;". "&amp;DAY('입력'!$C$13)&amp;".")&amp;" ("&amp;('입력'!$C$13-'입력'!$C$12+1)&amp;"일)")</f>
+        <f>IF(OR('입력'!$C$12="",'입력'!$C$92=""),"",IF('입력'!$C$12="","",YEAR('입력'!$C$12)&amp;". "&amp;MONTH('입력'!$C$12)&amp;". "&amp;DAY('입력'!$C$12)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$92="","",YEAR('입력'!$C$92)&amp;". "&amp;MONTH('입력'!$C$92)&amp;". "&amp;DAY('입력'!$C$92)&amp;".")&amp;" ("&amp;('입력'!$C$92-'입력'!$C$12+1)&amp;"일)")</f>
         <v/>
       </c>
       <c r="F7" s="39" t="n"/>
@@ -4450,7 +4450,7 @@
       <c r="C7" s="36" t="n"/>
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="38">
-        <f>IF(OR('입력'!$C$12="",'입력'!$C$13=""),"",IF('입력'!$C$12="","",YEAR('입력'!$C$12)&amp;". "&amp;MONTH('입력'!$C$12)&amp;". "&amp;DAY('입력'!$C$12)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$13="","",YEAR('입력'!$C$13)&amp;". "&amp;MONTH('입력'!$C$13)&amp;". "&amp;DAY('입력'!$C$13)&amp;".")&amp;" ("&amp;('입력'!$C$13-'입력'!$C$12+1)&amp;"일)")</f>
+        <f>IF(OR('입력'!$C$12="",'입력'!$C$92=""),"",IF('입력'!$C$12="","",YEAR('입력'!$C$12)&amp;". "&amp;MONTH('입력'!$C$12)&amp;". "&amp;DAY('입력'!$C$12)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$92="","",YEAR('입력'!$C$92)&amp;". "&amp;MONTH('입력'!$C$92)&amp;". "&amp;DAY('입력'!$C$92)&amp;".")&amp;" ("&amp;('입력'!$C$92-'입력'!$C$12+1)&amp;"일)")</f>
         <v/>
       </c>
       <c r="F7" s="39" t="n"/>
@@ -8244,7 +8244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O25"/>
+  <dimension ref="B1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="37.4" customHeight="1">
+    <row r="4" ht="35.7" customHeight="1">
       <c r="B4" s="35" t="inlineStr">
         <is>
           <t>공 사 명</t>
@@ -8305,7 +8305,7 @@
       <c r="L4" s="39" t="n"/>
       <c r="M4" s="40" t="n"/>
     </row>
-    <row r="5" ht="37.4" customHeight="1">
+    <row r="5" ht="35.7" customHeight="1">
       <c r="B5" s="35" t="inlineStr">
         <is>
           <t>현장 위치</t>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="37.4" customHeight="1">
+    <row r="6" ht="35.7" customHeight="1">
       <c r="B6" s="35" t="inlineStr">
         <is>
           <t>공사 개요</t>
@@ -8352,7 +8352,7 @@
       <c r="L6" s="39" t="n"/>
       <c r="M6" s="40" t="n"/>
     </row>
-    <row r="7" ht="28.6" customHeight="1">
+    <row r="7" ht="27.3" customHeight="1">
       <c r="B7" s="35" t="inlineStr">
         <is>
           <t>계약 방법</t>
@@ -8373,7 +8373,7 @@
       <c r="L7" s="39" t="n"/>
       <c r="M7" s="40" t="n"/>
     </row>
-    <row r="8" ht="28.6" customHeight="1">
+    <row r="8" ht="27.3" customHeight="1">
       <c r="B8" s="35" t="inlineStr">
         <is>
           <t>계약 번호</t>
@@ -8394,7 +8394,7 @@
       <c r="L8" s="39" t="n"/>
       <c r="M8" s="40" t="n"/>
     </row>
-    <row r="9" ht="28.6" customHeight="1">
+    <row r="9" ht="27.3" customHeight="1">
       <c r="B9" s="35" t="inlineStr">
         <is>
           <t>계 약 일</t>
@@ -8415,7 +8415,7 @@
       <c r="L9" s="39" t="n"/>
       <c r="M9" s="40" t="n"/>
     </row>
-    <row r="10" ht="28.6" customHeight="1">
+    <row r="10" ht="27.3" customHeight="1">
       <c r="B10" s="35" t="inlineStr">
         <is>
           <t>당초 계약금액</t>
@@ -8436,7 +8436,7 @@
       <c r="L10" s="39" t="n"/>
       <c r="M10" s="40" t="n"/>
     </row>
-    <row r="11" ht="28.6" customHeight="1">
+    <row r="11" ht="27.3" customHeight="1">
       <c r="B11" s="35" t="inlineStr">
         <is>
           <t>최종 계약금액</t>
@@ -8457,7 +8457,7 @@
       <c r="L11" s="39" t="n"/>
       <c r="M11" s="40" t="n"/>
     </row>
-    <row r="12" ht="28.6" customHeight="1">
+    <row r="12" ht="27.3" customHeight="1">
       <c r="B12" s="35" t="inlineStr">
         <is>
           <t>공사 기간</t>
@@ -8466,7 +8466,7 @@
       <c r="C12" s="36" t="n"/>
       <c r="D12" s="37" t="n"/>
       <c r="E12" s="38">
-        <f>IF(OR('입력'!$C$12="",'입력'!$C$13=""),"",IF('입력'!$C$12="","",YEAR('입력'!$C$12)&amp;". "&amp;MONTH('입력'!$C$12)&amp;". "&amp;DAY('입력'!$C$12)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$13="","",YEAR('입력'!$C$13)&amp;". "&amp;MONTH('입력'!$C$13)&amp;". "&amp;DAY('입력'!$C$13)&amp;".")&amp;" ("&amp;('입력'!$C$13-'입력'!$C$12+1)&amp;"일)")</f>
+        <f>IF(OR('입력'!$C$12="",'입력'!$C$92=""),"",IF('입력'!$C$12="","",YEAR('입력'!$C$12)&amp;". "&amp;MONTH('입력'!$C$12)&amp;". "&amp;DAY('입력'!$C$12)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$92="","",YEAR('입력'!$C$92)&amp;". "&amp;MONTH('입력'!$C$92)&amp;". "&amp;DAY('입력'!$C$92)&amp;".")&amp;" ("&amp;('입력'!$C$92-'입력'!$C$12+1)&amp;"일)")</f>
         <v/>
       </c>
       <c r="F12" s="39" t="n"/>
@@ -8478,16 +8478,16 @@
       <c r="L12" s="39" t="n"/>
       <c r="M12" s="40" t="n"/>
     </row>
-    <row r="13" ht="28.6" customHeight="1">
+    <row r="13" ht="27.3" customHeight="1">
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>준 공 일</t>
+          <t>공기 연장</t>
         </is>
       </c>
       <c r="C13" s="36" t="n"/>
       <c r="D13" s="37" t="n"/>
       <c r="E13" s="38">
-        <f>IF('입력'!$C$68="","",YEAR('입력'!$C$68)&amp;". "&amp;MONTH('입력'!$C$68)&amp;". "&amp;DAY('입력'!$C$68)&amp;".")</f>
+        <f>IF('입력'!$C$72="","없음","당초 "&amp;IF('입력'!$C$13="","",YEAR('입력'!$C$13)&amp;". "&amp;MONTH('입력'!$C$13)&amp;". "&amp;DAY('입력'!$C$13)&amp;".")&amp;" → 변경 "&amp;IF('입력'!$C$72="","",YEAR('입력'!$C$72)&amp;". "&amp;MONTH('입력'!$C$72)&amp;". "&amp;DAY('입력'!$C$72)&amp;".")&amp;" ("&amp;('입력'!$C$72-'입력'!$C$13)&amp;"일)")</f>
         <v/>
       </c>
       <c r="F13" s="39" t="n"/>
@@ -8499,16 +8499,16 @@
       <c r="L13" s="39" t="n"/>
       <c r="M13" s="40" t="n"/>
     </row>
-    <row r="14" ht="28.6" customHeight="1">
+    <row r="14" ht="27.3" customHeight="1">
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>준공검사일</t>
+          <t>준 공 일</t>
         </is>
       </c>
       <c r="C14" s="36" t="n"/>
       <c r="D14" s="37" t="n"/>
       <c r="E14" s="38">
-        <f>IF('입력'!$C$70="","",YEAR('입력'!$C$70)&amp;". "&amp;MONTH('입력'!$C$70)&amp;". "&amp;DAY('입력'!$C$70)&amp;".")</f>
+        <f>IF('입력'!$C$68="","",YEAR('입력'!$C$68)&amp;". "&amp;MONTH('입력'!$C$68)&amp;". "&amp;DAY('입력'!$C$68)&amp;".")</f>
         <v/>
       </c>
       <c r="F14" s="39" t="n"/>
@@ -8520,16 +8520,16 @@
       <c r="L14" s="39" t="n"/>
       <c r="M14" s="40" t="n"/>
     </row>
-    <row r="15" ht="37.4" customHeight="1">
+    <row r="15" ht="27.3" customHeight="1">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>계약상대자</t>
+          <t>준공검사일</t>
         </is>
       </c>
       <c r="C15" s="36" t="n"/>
       <c r="D15" s="37" t="n"/>
       <c r="E15" s="38">
-        <f>'입력'!$C$27&amp;IF('입력'!$C$28="",""," / 대표 "&amp;'입력'!$C$28)&amp;IF('입력'!$C$31="",""," / "&amp;'입력'!$C$31)</f>
+        <f>IF('입력'!$C$70="","",YEAR('입력'!$C$70)&amp;". "&amp;MONTH('입력'!$C$70)&amp;". "&amp;DAY('입력'!$C$70)&amp;".")</f>
         <v/>
       </c>
       <c r="F15" s="39" t="n"/>
@@ -8541,16 +8541,16 @@
       <c r="L15" s="39" t="n"/>
       <c r="M15" s="40" t="n"/>
     </row>
-    <row r="16" ht="28.6" customHeight="1">
+    <row r="16" ht="35.7" customHeight="1">
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>현장대리인</t>
+          <t>계약상대자</t>
         </is>
       </c>
       <c r="C16" s="36" t="n"/>
       <c r="D16" s="37" t="n"/>
       <c r="E16" s="38">
-        <f>'입력'!$C$38&amp;IF('입력'!$C$42="",""," / "&amp;'입력'!$C$42)</f>
+        <f>'입력'!$C$27&amp;IF('입력'!$C$28="",""," / 대표 "&amp;'입력'!$C$28)&amp;IF('입력'!$C$31="",""," / "&amp;'입력'!$C$31)</f>
         <v/>
       </c>
       <c r="F16" s="39" t="n"/>
@@ -8562,16 +8562,16 @@
       <c r="L16" s="39" t="n"/>
       <c r="M16" s="40" t="n"/>
     </row>
-    <row r="17" ht="28.6" customHeight="1">
+    <row r="17" ht="27.3" customHeight="1">
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>설 계 자</t>
+          <t>현장대리인</t>
         </is>
       </c>
       <c r="C17" s="36" t="n"/>
       <c r="D17" s="37" t="n"/>
       <c r="E17" s="38">
-        <f>'입력'!$C$23&amp;""</f>
+        <f>'입력'!$C$38&amp;IF('입력'!$C$42="",""," / "&amp;'입력'!$C$42)</f>
         <v/>
       </c>
       <c r="F17" s="39" t="n"/>
@@ -8583,16 +8583,16 @@
       <c r="L17" s="39" t="n"/>
       <c r="M17" s="40" t="n"/>
     </row>
-    <row r="18" ht="28.6" customHeight="1">
+    <row r="18" ht="27.3" customHeight="1">
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>감 리 자</t>
+          <t>설 계 자</t>
         </is>
       </c>
       <c r="C18" s="36" t="n"/>
       <c r="D18" s="37" t="n"/>
       <c r="E18" s="38">
-        <f>'입력'!$C$24&amp;""</f>
+        <f>'입력'!$C$23&amp;""</f>
         <v/>
       </c>
       <c r="F18" s="39" t="n"/>
@@ -8604,16 +8604,16 @@
       <c r="L18" s="39" t="n"/>
       <c r="M18" s="40" t="n"/>
     </row>
-    <row r="19" ht="28.6" customHeight="1">
+    <row r="19" ht="27.3" customHeight="1">
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>공사 감독자</t>
+          <t>감 리 자</t>
         </is>
       </c>
       <c r="C19" s="36" t="n"/>
       <c r="D19" s="37" t="n"/>
       <c r="E19" s="38">
-        <f>'입력'!$C$20&amp;""</f>
+        <f>'입력'!$C$24&amp;""</f>
         <v/>
       </c>
       <c r="F19" s="39" t="n"/>
@@ -8625,16 +8625,16 @@
       <c r="L19" s="39" t="n"/>
       <c r="M19" s="40" t="n"/>
     </row>
-    <row r="20" ht="28.6" customHeight="1">
+    <row r="20" ht="27.3" customHeight="1">
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>계약보증</t>
+          <t>공사 감독자</t>
         </is>
       </c>
       <c r="C20" s="36" t="n"/>
       <c r="D20" s="37" t="n"/>
       <c r="E20" s="38">
-        <f>IF('입력'!$C$86="",'입력'!$C$46&amp;"",FIXED('입력'!$C$86,0)&amp;"원 / "&amp;'입력'!$C$46)</f>
+        <f>'입력'!$C$20&amp;""</f>
         <v/>
       </c>
       <c r="F20" s="39" t="n"/>
@@ -8646,16 +8646,16 @@
       <c r="L20" s="39" t="n"/>
       <c r="M20" s="40" t="n"/>
     </row>
-    <row r="21" ht="28.6" customHeight="1">
+    <row r="21" ht="27.3" customHeight="1">
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>하자보수보증</t>
+          <t>계약보증</t>
         </is>
       </c>
       <c r="C21" s="36" t="n"/>
       <c r="D21" s="37" t="n"/>
       <c r="E21" s="38">
-        <f>IF('입력'!$C$88="",'입력'!$C$49&amp;"",FIXED('입력'!$C$88,0)&amp;"원 / "&amp;'입력'!$C$49)</f>
+        <f>IF('입력'!$C$86="",'입력'!$C$46&amp;"",FIXED('입력'!$C$86,0)&amp;"원 / "&amp;'입력'!$C$46)</f>
         <v/>
       </c>
       <c r="F21" s="39" t="n"/>
@@ -8667,16 +8667,16 @@
       <c r="L21" s="39" t="n"/>
       <c r="M21" s="40" t="n"/>
     </row>
-    <row r="22" ht="28.6" customHeight="1">
+    <row r="22" ht="27.3" customHeight="1">
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>하자담보책임기간</t>
+          <t>하자보수보증</t>
         </is>
       </c>
       <c r="C22" s="36" t="n"/>
       <c r="D22" s="37" t="n"/>
       <c r="E22" s="38">
-        <f>IF('입력'!$C$91="","",IF('입력'!$C$90="","",YEAR('입력'!$C$90)&amp;". "&amp;MONTH('입력'!$C$90)&amp;". "&amp;DAY('입력'!$C$90)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$91="","",YEAR('입력'!$C$91)&amp;". "&amp;MONTH('입력'!$C$91)&amp;". "&amp;DAY('입력'!$C$91)&amp;"."))</f>
+        <f>IF('입력'!$C$88="",'입력'!$C$49&amp;"",FIXED('입력'!$C$88,0)&amp;"원 / "&amp;'입력'!$C$49)</f>
         <v/>
       </c>
       <c r="F22" s="39" t="n"/>
@@ -8688,16 +8688,16 @@
       <c r="L22" s="39" t="n"/>
       <c r="M22" s="40" t="n"/>
     </row>
-    <row r="23" ht="28.6" customHeight="1">
+    <row r="23" ht="27.3" customHeight="1">
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>지체 일수·상금</t>
+          <t>하자담보책임기간</t>
         </is>
       </c>
       <c r="C23" s="36" t="n"/>
       <c r="D23" s="37" t="n"/>
       <c r="E23" s="38">
-        <f>IF('입력'!$C$93="","",IF('입력'!$C$93=0,"없음",'입력'!$C$93&amp;"일 / "&amp;FIXED(N('입력'!$C$95),0)&amp;"원"))</f>
+        <f>IF('입력'!$C$91="","",IF('입력'!$C$90="","",YEAR('입력'!$C$90)&amp;". "&amp;MONTH('입력'!$C$90)&amp;". "&amp;DAY('입력'!$C$90)&amp;".")&amp;" ~ "&amp;IF('입력'!$C$91="","",YEAR('입력'!$C$91)&amp;". "&amp;MONTH('입력'!$C$91)&amp;". "&amp;DAY('입력'!$C$91)&amp;"."))</f>
         <v/>
       </c>
       <c r="F23" s="39" t="n"/>
@@ -8709,16 +8709,37 @@
       <c r="L23" s="39" t="n"/>
       <c r="M23" s="40" t="n"/>
     </row>
-    <row r="24" ht="8" customHeight="1"/>
-    <row r="25" ht="22.725" customHeight="1">
-      <c r="B25" s="50" t="inlineStr">
+    <row r="24" ht="27.3" customHeight="1">
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>지체 일수·상금</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="38">
+        <f>IF('입력'!$C$93="","",IF('입력'!$C$93=0,"없음",'입력'!$C$93&amp;"일 / "&amp;FIXED(N('입력'!$C$95),0)&amp;"원"))</f>
+        <v/>
+      </c>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="39" t="n"/>
+      <c r="K24" s="39" t="n"/>
+      <c r="L24" s="39" t="n"/>
+      <c r="M24" s="40" t="n"/>
+    </row>
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22.725" customHeight="1">
+      <c r="B26" s="50" t="inlineStr">
         <is>
           <t>※ 공사 하나에 한 장 — 계약부터 하자까지 한눈에 보는 관리 카드입니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="44">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B14:D14"/>
@@ -8738,6 +8759,7 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E16:M16"/>
     <mergeCell ref="E7:M7"/>
@@ -8745,11 +8767,12 @@
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="E22:M22"/>
     <mergeCell ref="E18:M18"/>
+    <mergeCell ref="B26:M26"/>
     <mergeCell ref="E21:M21"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="E12:M12"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B25:M25"/>
+    <mergeCell ref="E24:M24"/>
     <mergeCell ref="E5:M5"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="E23:M23"/>
@@ -11706,7 +11729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O31"/>
+  <dimension ref="B1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -11746,7 +11769,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="35.8" customHeight="1">
+    <row r="4" ht="34" customHeight="1">
       <c r="B4" s="35" t="inlineStr">
         <is>
           <t>공 사 명</t>
@@ -11767,7 +11790,7 @@
       <c r="L4" s="39" t="n"/>
       <c r="M4" s="40" t="n"/>
     </row>
-    <row r="5" ht="27.4" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="B5" s="35" t="inlineStr">
         <is>
           <t>계약 번호</t>
@@ -11793,7 +11816,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="27.4" customHeight="1">
+    <row r="6" ht="26" customHeight="1">
       <c r="B6" s="35" t="inlineStr">
         <is>
           <t>계 약 일</t>
@@ -11814,7 +11837,7 @@
       <c r="L6" s="39" t="n"/>
       <c r="M6" s="40" t="n"/>
     </row>
-    <row r="7" ht="35.8" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="B7" s="35" t="inlineStr">
         <is>
           <t>계약 금액</t>
@@ -11835,7 +11858,7 @@
       <c r="L7" s="39" t="n"/>
       <c r="M7" s="40" t="n"/>
     </row>
-    <row r="8" ht="27.4" customHeight="1">
+    <row r="8" ht="26" customHeight="1">
       <c r="B8" s="35" t="inlineStr">
         <is>
           <t>공사 기간</t>
@@ -11856,7 +11879,7 @@
       <c r="L8" s="39" t="n"/>
       <c r="M8" s="40" t="n"/>
     </row>
-    <row r="9" ht="27.4" customHeight="1">
+    <row r="9" ht="26" customHeight="1">
       <c r="B9" s="35" t="inlineStr">
         <is>
           <t>착 공 일</t>
@@ -11877,7 +11900,7 @@
       <c r="L9" s="39" t="n"/>
       <c r="M9" s="40" t="n"/>
     </row>
-    <row r="10" ht="27.4" customHeight="1">
+    <row r="10" ht="26" customHeight="1">
       <c r="B10" s="35" t="inlineStr">
         <is>
           <t>준공 기한</t>
@@ -11898,7 +11921,7 @@
       <c r="L10" s="39" t="n"/>
       <c r="M10" s="40" t="n"/>
     </row>
-    <row r="11" ht="35.8" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="B11" s="35" t="inlineStr">
         <is>
           <t>현장 위치</t>
@@ -11919,7 +11942,7 @@
       <c r="L11" s="39" t="n"/>
       <c r="M11" s="40" t="n"/>
     </row>
-    <row r="12" ht="27.4" customHeight="1">
+    <row r="12" ht="26" customHeight="1">
       <c r="B12" s="35" t="inlineStr">
         <is>
           <t>현장대리인</t>
@@ -11974,10 +11997,10 @@
       <c r="L15" s="36" t="n"/>
       <c r="M15" s="37" t="n"/>
     </row>
-    <row r="16" ht="23.2" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="B16" s="42" t="inlineStr">
         <is>
-          <t>현장대리인 지정 신고서</t>
+          <t>현장기술자 지정신고서 (현장대리인)</t>
         </is>
       </c>
       <c r="C16" s="39" t="n"/>
@@ -11996,10 +12019,10 @@
       <c r="L16" s="39" t="n"/>
       <c r="M16" s="40" t="n"/>
     </row>
-    <row r="17" ht="23.2" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="B17" s="42" t="inlineStr">
         <is>
-          <t>공사 예정공정표</t>
+          <t>공사공정예정표</t>
         </is>
       </c>
       <c r="C17" s="39" t="n"/>
@@ -12018,10 +12041,10 @@
       <c r="L17" s="39" t="n"/>
       <c r="M17" s="40" t="n"/>
     </row>
-    <row r="18" ht="23.2" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="B18" s="42" t="inlineStr">
         <is>
-          <t>직접시공계획서 (해당 시)</t>
+          <t>안전·환경 및 품질관리계획서</t>
         </is>
       </c>
       <c r="C18" s="39" t="n"/>
@@ -12040,10 +12063,10 @@
       <c r="L18" s="39" t="n"/>
       <c r="M18" s="40" t="n"/>
     </row>
-    <row r="19" ht="23.2" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>안전·보건 관리 계획서 (해당 시)</t>
+          <t>공정별 인력 및 장비투입계획서</t>
         </is>
       </c>
       <c r="C19" s="39" t="n"/>
@@ -12062,10 +12085,10 @@
       <c r="L19" s="39" t="n"/>
       <c r="M19" s="40" t="n"/>
     </row>
-    <row r="20" ht="23.2" customHeight="1">
+    <row r="20" ht="22" customHeight="1">
       <c r="B20" s="42" t="inlineStr">
         <is>
-          <t>착공 전 현장 사진</t>
+          <t>착공 전 현장사진</t>
         </is>
       </c>
       <c r="C20" s="39" t="n"/>
@@ -12084,97 +12107,113 @@
       <c r="L20" s="39" t="n"/>
       <c r="M20" s="40" t="n"/>
     </row>
-    <row r="21" ht="23.2" customHeight="1">
-      <c r="B21" s="42" t="n"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>그 밖에 발주기관이 정한 서류 (직접시공계획서 등)</t>
+        </is>
+      </c>
       <c r="C21" s="39" t="n"/>
       <c r="D21" s="39" t="n"/>
       <c r="E21" s="39" t="n"/>
       <c r="F21" s="39" t="n"/>
       <c r="G21" s="39" t="n"/>
       <c r="H21" s="40" t="n"/>
-      <c r="I21" s="42" t="n"/>
+      <c r="I21" s="42" t="inlineStr">
+        <is>
+          <t>1부</t>
+        </is>
+      </c>
       <c r="J21" s="40" t="n"/>
       <c r="K21" s="42" t="n"/>
       <c r="L21" s="39" t="n"/>
       <c r="M21" s="40" t="n"/>
     </row>
     <row r="22" ht="8" customHeight="1"/>
-    <row r="23" ht="8" customHeight="1"/>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="44">
+    <row r="23" ht="37.45" customHeight="1">
+      <c r="B23" s="50" t="inlineStr">
+        <is>
+          <t>※ 붙임은 공사계약일반조건 제17조①(착공신고서) 그대로입니다. 공사기간 30일 미만 등은 발주기관이 내지 않게 할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="44">
         <f>IF('입력'!$C$12="","          년      월      일",YEAR('입력'!$C$12)&amp;"년  "&amp;MONTH('입력'!$C$12)&amp;"월  "&amp;DAY('입력'!$C$12)&amp;"일")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="45" t="inlineStr">
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="24" customHeight="1">
+      <c r="B27" s="45" t="inlineStr">
         <is>
           <t>계약상대자</t>
         </is>
       </c>
-      <c r="G26" s="46" t="inlineStr">
+      <c r="G27" s="46" t="inlineStr">
         <is>
           <t>상    호</t>
         </is>
       </c>
-      <c r="I26" s="47" t="inlineStr">
+      <c r="I27" s="47" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="J26" s="48">
+      <c r="J27" s="48">
         <f>'입력'!$C$27&amp;""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="G27" s="46" t="inlineStr">
-        <is>
-          <t>주    소</t>
-        </is>
-      </c>
-      <c r="I27" s="47" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="J27" s="48">
-        <f>'입력'!$C$30&amp;""</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="G28" s="46" t="inlineStr">
         <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="I28" s="47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="J28" s="48">
+        <f>'입력'!$C$30&amp;""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="G29" s="46" t="inlineStr">
+        <is>
           <t>대 표 자</t>
         </is>
       </c>
-      <c r="I28" s="47" t="inlineStr">
+      <c r="I29" s="47" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="J28" s="48">
+      <c r="J29" s="48">
         <f>'입력'!$C$28&amp;"          (인)"</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="8" customHeight="1"/>
     <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="49">
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="49">
         <f>IF('입력'!$C$18="","                  귀하",'입력'!$C$18&amp;"  귀하")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="51">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E10:M10"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B23:M23"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="B14:M14"/>
     <mergeCell ref="E9:M9"/>
@@ -12182,37 +12221,37 @@
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="E6:M6"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B26:E26"/>
     <mergeCell ref="E11:M11"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="K17:M17"/>
+    <mergeCell ref="J29:M29"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B24:M24"/>
     <mergeCell ref="J28:M28"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="K19:M19"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B32:M32"/>
     <mergeCell ref="K18:M18"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="K16:M16"/>
     <mergeCell ref="E12:M12"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="G26:H26"/>
     <mergeCell ref="K15:M15"/>
     <mergeCell ref="J27:M27"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="B25:M25"/>
     <mergeCell ref="E5:M5"/>
-    <mergeCell ref="B31:M31"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="K21:M21"/>
     <mergeCell ref="E8:M8"/>

--- a/web/public/tools/files/k-conmap-wonclick.xlsx
+++ b/web/public/tools/files/k-conmap-wonclick.xlsx
@@ -48,7 +48,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'처음'!$A$1:$G$54</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'입력'!$A$1:$D$146</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'입력'!$A$1:$D$147</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'01 사용인감계'!$A$1:$M$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'02 계약보증금 납부서'!$A$1:$M$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'03 계약보증금 지급각서'!$A$1:$M$18</definedName>
@@ -3062,7 +3062,7 @@
       <c r="M18" s="40" t="n"/>
     </row>
     <row r="19" ht="8" customHeight="1"/>
-    <row r="20" ht="10.09999999999991" customHeight="1"/>
+    <row r="20" ht="10.10000000000002" customHeight="1"/>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="44">
         <f>IF('입력'!$C$12="","          년      월      일",YEAR('입력'!$C$12)&amp;"년  "&amp;MONTH('입력'!$C$12)&amp;"월  "&amp;DAY('입력'!$C$12)&amp;"일")</f>
@@ -7375,7 +7375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D145"/>
+  <dimension ref="B1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -8024,7 +8024,11 @@
         </is>
       </c>
       <c r="C68" s="23" t="n"/>
-      <c r="D68" s="22" t="n"/>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>준공신고서에 적는 준공일</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
@@ -8046,7 +8050,11 @@
         </is>
       </c>
       <c r="C70" s="23" t="n"/>
-      <c r="D70" s="22" t="n"/>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>보완 요구였으면 최종 합격한 날 — 관급은 준공기한을 넘겨 신고하면 이날까지가 지체일수</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
@@ -8118,7 +8126,7 @@
       <c r="C76" s="24" t="n"/>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>비우면 자동 계산(최종 계약금액×요율×지체일수). 면제·감면·기성 인수분 공제가 있으면 그 금액(0 포함)을 넣으세요</t>
+          <t>비우면 자동 계산 — 최종 계약금액×요율×지체일수 · 관급은 계약금액의 30% 까지(국가계약법 시행령 제74조 ③). 면제·감면·기성 인수분 공제가 있으면 그 금액(0 포함)을 넣으세요</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8631,7 @@
         </is>
       </c>
       <c r="C129" s="31">
-        <f>IF(OR('입력'!$C$128="",'입력'!$C$48=""),"",EDATE('입력'!$C$128,'입력'!$C$48*12)-1)</f>
+        <f>IF(OR('입력'!$C$128="",'입력'!$C$48=""),"",IF(DAY(EDATE('입력'!$C$128,'입력'!$C$48*12))&lt;&gt;DAY('입력'!$C$128),EDATE('입력'!$C$128,'입력'!$C$48*12),EDATE('입력'!$C$128,'입력'!$C$48*12)-1))</f>
         <v/>
       </c>
     </row>
@@ -8645,7 +8653,7 @@
         </is>
       </c>
       <c r="C131" s="29">
-        <f>IF(OR('입력'!$C$68="",'입력'!$C$130=""),"",MAX(0,'입력'!$C$68-'입력'!$C$130))</f>
+        <f>IF(OR('입력'!$C$68="",'입력'!$C$130=""),"",IF('입력'!$C$10="민간계약",MAX(0,'입력'!$C$68-'입력'!$C$130),IF('입력'!$C$127&lt;='입력'!$C$130,0,MAX(0,IF('입력'!$C$70="",'입력'!$C$127,'입력'!$C$70)-'입력'!$C$130))))</f>
         <v/>
       </c>
     </row>
@@ -8656,7 +8664,7 @@
         </is>
       </c>
       <c r="C132" s="30">
-        <f>IF(OR('입력'!$C$131="",'입력'!$C$50=""),"",ROUNDDOWN('입력'!$C$125*'입력'!$C$50/1000*'입력'!$C$131,0))</f>
+        <f>IF(OR('입력'!$C$131="",'입력'!$C$50=""),"",IF('입력'!$C$146="",ROUNDDOWN('입력'!$C$125*'입력'!$C$50/1000*'입력'!$C$131,0),MIN(ROUNDDOWN('입력'!$C$125*'입력'!$C$50/1000*'입력'!$C$131,0),'입력'!$C$146)))</f>
         <v/>
       </c>
     </row>
@@ -8800,6 +8808,17 @@
       </c>
       <c r="C145" s="30">
         <f>IF(OR('입력'!$C$14="",'입력'!$C$119=""),"",'입력'!$C$14+IF('입력'!$C$118="감액",-1,1)*'입력'!$C$119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="B146" s="28" t="inlineStr">
+        <is>
+          <t>지체상금 한도 (관급 — 계약금액의 30%)</t>
+        </is>
+      </c>
+      <c r="C146" s="30">
+        <f>IF('입력'!$C$125="","",IF('입력'!$C$10="민간계약","",ROUNDDOWN('입력'!$C$125*0.3,0)))</f>
         <v/>
       </c>
     </row>
@@ -10805,7 +10824,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="53.42499999999995" customHeight="1"/>
+    <row r="19" ht="53.42500000000007" customHeight="1"/>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="44">
         <f>IF('입력'!$C$137="","          년      월      일",YEAR('입력'!$C$137)&amp;"년  "&amp;MONTH('입력'!$C$137)&amp;"월  "&amp;DAY('입력'!$C$137)&amp;"일")</f>
@@ -11707,7 +11726,7 @@
       <c r="M15" s="40" t="n"/>
     </row>
     <row r="16" ht="8" customHeight="1"/>
-    <row r="17" ht="60.14999999999986" customHeight="1"/>
+    <row r="17" ht="60.14999999999998" customHeight="1"/>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="44">
         <f>IF('입력'!$C$63="","          년      월      일",YEAR('입력'!$C$63)&amp;"년  "&amp;MONTH('입력'!$C$63)&amp;"월  "&amp;DAY('입력'!$C$63)&amp;"일")</f>
@@ -12838,7 +12857,7 @@
       <c r="M19" s="40" t="n"/>
     </row>
     <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="8.250000000000114" customHeight="1"/>
+    <row r="21" ht="8.25" customHeight="1"/>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="44">
         <f>IF('입력'!$C$68="","          년      월      일",YEAR('입력'!$C$68)&amp;"년  "&amp;MONTH('입력'!$C$68)&amp;"월  "&amp;DAY('입력'!$C$68)&amp;"일")</f>
@@ -13586,7 +13605,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="8.549999999999955" customHeight="1"/>
+    <row r="20" ht="8.550000000000068" customHeight="1"/>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="44">
         <f>IF('입력'!$C$139="","          년      월      일",YEAR('입력'!$C$139)&amp;"년  "&amp;MONTH('입력'!$C$139)&amp;"월  "&amp;DAY('입력'!$C$139)&amp;"일")</f>
@@ -15575,7 +15594,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="124.8999999999999" customHeight="1"/>
+    <row r="15" ht="124.9" customHeight="1"/>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="44">
         <f>IF('입력'!$C$70="","          년      월      일",YEAR('입력'!$C$70)&amp;"년  "&amp;MONTH('입력'!$C$70)&amp;"월  "&amp;DAY('입력'!$C$70)&amp;"일")</f>
@@ -17955,7 +17974,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="99.82499999999993" customHeight="1"/>
+    <row r="17" ht="99.82500000000005" customHeight="1"/>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="44">
         <f>IF('입력'!$C$11="","          년      월      일",YEAR('입력'!$C$11)&amp;"년  "&amp;MONTH('입력'!$C$11)&amp;"월  "&amp;DAY('입력'!$C$11)&amp;"일")</f>
@@ -19198,7 +19217,7 @@
       <c r="M18" s="40" t="n"/>
     </row>
     <row r="19" ht="8" customHeight="1"/>
-    <row r="20" ht="18.34999999999991" customHeight="1"/>
+    <row r="20" ht="18.35000000000002" customHeight="1"/>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="44">
         <f>IF('입력'!$C$85="","          년      월      일",YEAR('입력'!$C$85)&amp;"년  "&amp;MONTH('입력'!$C$85)&amp;"월  "&amp;DAY('입력'!$C$85)&amp;"일")</f>
@@ -19642,7 +19661,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="8.149999999999864" customHeight="1"/>
+    <row r="22" ht="8.149999999999977" customHeight="1"/>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="44">
         <f>IF('입력'!$C$85="","          년      월      일",YEAR('입력'!$C$85)&amp;"년  "&amp;MONTH('입력'!$C$85)&amp;"월  "&amp;DAY('입력'!$C$85)&amp;"일")</f>
